--- a/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
@@ -436,37 +436,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="C1" s="1">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="D1" s="1">
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="E1" s="1">
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="F1" s="1">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="G1" s="1">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H1" s="1">
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="I1" s="1">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="J1" s="1">
-        <v>46134</v>
+        <v>46155</v>
       </c>
       <c r="K1" s="1">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="L1" s="1">
-        <v>46148</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -474,37 +474,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>17.4</v>
+        <v>24.7</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>28.6</v>
       </c>
       <c r="D2">
-        <v>20.8</v>
+        <v>33.2</v>
       </c>
       <c r="E2">
-        <v>22.7</v>
+        <v>38.5</v>
       </c>
       <c r="F2">
-        <v>24.8</v>
+        <v>44.3</v>
       </c>
       <c r="G2">
-        <v>27</v>
+        <v>50.5</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>56.8</v>
       </c>
       <c r="I2">
-        <v>30.9</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>32.7</v>
+        <v>69</v>
       </c>
       <c r="K2">
-        <v>34.3</v>
+        <v>74.3</v>
       </c>
       <c r="L2">
-        <v>35.7</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -512,37 +512,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>23.2</v>
+        <v>33.7</v>
       </c>
       <c r="C3">
-        <v>25.7</v>
+        <v>38.5</v>
       </c>
       <c r="D3">
-        <v>28.3</v>
+        <v>43.8</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>49.7</v>
       </c>
       <c r="F3">
-        <v>33.7</v>
+        <v>55.9</v>
       </c>
       <c r="G3">
-        <v>36.2</v>
+        <v>62.3</v>
       </c>
       <c r="H3">
-        <v>38.4</v>
+        <v>68.7</v>
       </c>
       <c r="I3">
-        <v>40.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J3">
-        <v>42.1</v>
+        <v>80.7</v>
       </c>
       <c r="K3">
-        <v>43.5</v>
+        <v>85.7</v>
       </c>
       <c r="L3">
-        <v>44.7</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -550,37 +550,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>10.8</v>
+        <v>19.1</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>22.8</v>
       </c>
       <c r="D4">
-        <v>15.4</v>
+        <v>26.7</v>
       </c>
       <c r="E4">
-        <v>18.1</v>
+        <v>30.9</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>35.2</v>
       </c>
       <c r="G4">
-        <v>23.9</v>
+        <v>39.7</v>
       </c>
       <c r="H4">
-        <v>26.9</v>
+        <v>44</v>
       </c>
       <c r="I4">
-        <v>29.7</v>
+        <v>48.2</v>
       </c>
       <c r="J4">
-        <v>32.5</v>
+        <v>52</v>
       </c>
       <c r="K4">
-        <v>35.1</v>
+        <v>55.4</v>
       </c>
       <c r="L4">
-        <v>37.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -588,37 +588,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>11.8</v>
+        <v>18.8</v>
       </c>
       <c r="C5">
-        <v>13.6</v>
+        <v>22.1</v>
       </c>
       <c r="D5">
-        <v>15.9</v>
+        <v>25.9</v>
       </c>
       <c r="E5">
-        <v>18.5</v>
+        <v>29.9</v>
       </c>
       <c r="F5">
-        <v>21.4</v>
+        <v>34.2</v>
       </c>
       <c r="G5">
-        <v>24.6</v>
+        <v>38.5</v>
       </c>
       <c r="H5">
-        <v>28</v>
+        <v>42.8</v>
       </c>
       <c r="I5">
-        <v>31.4</v>
+        <v>46.9</v>
       </c>
       <c r="J5">
-        <v>34.8</v>
+        <v>50.6</v>
       </c>
       <c r="K5">
-        <v>38.1</v>
+        <v>53.8</v>
       </c>
       <c r="L5">
-        <v>41.1</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -626,37 +626,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>23.2</v>
+        <v>31.8</v>
       </c>
       <c r="C6">
-        <v>24.3</v>
+        <v>37.6</v>
       </c>
       <c r="D6">
-        <v>25.7</v>
+        <v>44.8</v>
       </c>
       <c r="E6">
-        <v>27.4</v>
+        <v>53.3</v>
       </c>
       <c r="F6">
-        <v>29.2</v>
+        <v>63</v>
       </c>
       <c r="G6">
-        <v>30.9</v>
+        <v>73.5</v>
       </c>
       <c r="H6">
-        <v>32.5</v>
+        <v>84.5</v>
       </c>
       <c r="I6">
-        <v>33.8</v>
+        <v>95.5</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>106.1</v>
       </c>
       <c r="K6">
-        <v>35.9</v>
+        <v>115.8</v>
       </c>
       <c r="L6">
-        <v>36.7</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -664,37 +664,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>23.9</v>
+        <v>34.2</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>39.4</v>
       </c>
       <c r="D7">
-        <v>28.1</v>
+        <v>45.4</v>
       </c>
       <c r="E7">
-        <v>30.1</v>
+        <v>52.3</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>33.6</v>
+        <v>68.2</v>
       </c>
       <c r="H7">
-        <v>34.9</v>
+        <v>76.7</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>85.2</v>
       </c>
       <c r="J7">
-        <v>36.9</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K7">
-        <v>37.7</v>
+        <v>100.7</v>
       </c>
       <c r="L7">
-        <v>38.4</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -702,37 +702,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>8.6</v>
+        <v>18.3</v>
       </c>
       <c r="C8">
-        <v>10.5</v>
+        <v>24.1</v>
       </c>
       <c r="D8">
-        <v>12.8</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>15.4</v>
+        <v>38.9</v>
       </c>
       <c r="F8">
-        <v>18.4</v>
+        <v>47.8</v>
       </c>
       <c r="G8">
-        <v>21.6</v>
+        <v>57.2</v>
       </c>
       <c r="H8">
-        <v>24.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J8">
-        <v>31.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K8">
-        <v>33.9</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L8">
-        <v>36.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -740,37 +740,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>19.8</v>
+        <v>29.7</v>
       </c>
       <c r="C9">
-        <v>21.9</v>
+        <v>34.8</v>
       </c>
       <c r="D9">
-        <v>24.2</v>
+        <v>40.7</v>
       </c>
       <c r="E9">
-        <v>26.6</v>
+        <v>47.4</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>54.8</v>
       </c>
       <c r="G9">
-        <v>31.3</v>
+        <v>62.7</v>
       </c>
       <c r="H9">
-        <v>33.5</v>
+        <v>70.8</v>
       </c>
       <c r="I9">
-        <v>35.5</v>
+        <v>78.7</v>
       </c>
       <c r="J9">
-        <v>37.4</v>
+        <v>86.2</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L9">
-        <v>40.5</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -778,37 +778,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>12.7</v>
+        <v>16.8</v>
       </c>
       <c r="C10">
-        <v>13.9</v>
+        <v>18.7</v>
       </c>
       <c r="D10">
-        <v>15.3</v>
+        <v>20.9</v>
       </c>
       <c r="E10">
-        <v>16.9</v>
+        <v>23.3</v>
       </c>
       <c r="F10">
-        <v>18.8</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>20.8</v>
+        <v>28.9</v>
       </c>
       <c r="H10">
-        <v>22.9</v>
+        <v>31.9</v>
       </c>
       <c r="I10">
-        <v>25.1</v>
+        <v>35</v>
       </c>
       <c r="J10">
-        <v>27.5</v>
+        <v>38</v>
       </c>
       <c r="K10">
-        <v>29.8</v>
+        <v>40.9</v>
       </c>
       <c r="L10">
-        <v>32.1</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -816,37 +816,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>9.300000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>26.9</v>
       </c>
       <c r="D11">
-        <v>13.1</v>
+        <v>35.1</v>
       </c>
       <c r="E11">
-        <v>15.6</v>
+        <v>44.6</v>
       </c>
       <c r="F11">
-        <v>18.3</v>
+        <v>55.3</v>
       </c>
       <c r="G11">
-        <v>21</v>
+        <v>66.7</v>
       </c>
       <c r="H11">
-        <v>23.6</v>
+        <v>78.5</v>
       </c>
       <c r="I11">
-        <v>26</v>
+        <v>90.2</v>
       </c>
       <c r="J11">
-        <v>28.2</v>
+        <v>101.3</v>
       </c>
       <c r="K11">
-        <v>30.2</v>
+        <v>111.3</v>
       </c>
       <c r="L11">
-        <v>32.1</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -854,37 +854,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>18</v>
+        <v>26.2</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>29.9</v>
       </c>
       <c r="D12">
-        <v>22.1</v>
+        <v>34</v>
       </c>
       <c r="E12">
-        <v>24.2</v>
+        <v>38.4</v>
       </c>
       <c r="F12">
-        <v>26.4</v>
+        <v>43</v>
       </c>
       <c r="G12">
-        <v>28.4</v>
+        <v>47.9</v>
       </c>
       <c r="H12">
-        <v>30.4</v>
+        <v>52.9</v>
       </c>
       <c r="I12">
-        <v>32.2</v>
+        <v>57.7</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>62.2</v>
       </c>
       <c r="K12">
-        <v>35.6</v>
+        <v>66.2</v>
       </c>
       <c r="L12">
-        <v>37.1</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -892,37 +892,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>29.1</v>
+        <v>39.3</v>
       </c>
       <c r="C13">
-        <v>31.6</v>
+        <v>43.9</v>
       </c>
       <c r="D13">
-        <v>34.4</v>
+        <v>48.8</v>
       </c>
       <c r="E13">
-        <v>37.3</v>
+        <v>54.1</v>
       </c>
       <c r="F13">
-        <v>40.1</v>
+        <v>59.5</v>
       </c>
       <c r="G13">
-        <v>42.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H13">
-        <v>45.3</v>
+        <v>70.2</v>
       </c>
       <c r="I13">
-        <v>47.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J13">
-        <v>49.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K13">
-        <v>50.6</v>
+        <v>83.3</v>
       </c>
       <c r="L13">
-        <v>51.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -930,37 +930,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>20.7</v>
+        <v>26.7</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>29.8</v>
       </c>
       <c r="D14">
-        <v>23.2</v>
+        <v>33.4</v>
       </c>
       <c r="E14">
-        <v>24.4</v>
+        <v>37.5</v>
       </c>
       <c r="F14">
-        <v>25.2</v>
+        <v>41.9</v>
       </c>
       <c r="G14">
-        <v>25.7</v>
+        <v>46.7</v>
       </c>
       <c r="H14">
-        <v>25.8</v>
+        <v>51.8</v>
       </c>
       <c r="I14">
-        <v>25.4</v>
+        <v>57</v>
       </c>
       <c r="J14">
-        <v>24.7</v>
+        <v>62.2</v>
       </c>
       <c r="K14">
-        <v>23.9</v>
+        <v>67.2</v>
       </c>
       <c r="L14">
-        <v>23</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -968,37 +968,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>22.6</v>
+        <v>32.4</v>
       </c>
       <c r="C15">
-        <v>24.7</v>
+        <v>37.2</v>
       </c>
       <c r="D15">
-        <v>26.7</v>
+        <v>42.8</v>
       </c>
       <c r="E15">
-        <v>28.7</v>
+        <v>49.2</v>
       </c>
       <c r="F15">
-        <v>30.5</v>
+        <v>56.2</v>
       </c>
       <c r="G15">
-        <v>32.2</v>
+        <v>63.8</v>
       </c>
       <c r="H15">
-        <v>33.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I15">
-        <v>34.9</v>
+        <v>79.5</v>
       </c>
       <c r="J15">
-        <v>36</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K15">
-        <v>37.1</v>
+        <v>93.7</v>
       </c>
       <c r="L15">
-        <v>38.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1006,37 +1006,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>9.800000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D16">
-        <v>12.6</v>
+        <v>23.2</v>
       </c>
       <c r="E16">
-        <v>14.4</v>
+        <v>28.1</v>
       </c>
       <c r="F16">
-        <v>16.5</v>
+        <v>33.5</v>
       </c>
       <c r="G16">
-        <v>18.9</v>
+        <v>39.4</v>
       </c>
       <c r="H16">
-        <v>21.5</v>
+        <v>45.4</v>
       </c>
       <c r="I16">
-        <v>24.2</v>
+        <v>51.4</v>
       </c>
       <c r="J16">
-        <v>26.9</v>
+        <v>57</v>
       </c>
       <c r="K16">
-        <v>29.5</v>
+        <v>62.1</v>
       </c>
       <c r="L16">
-        <v>31.9</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1044,37 +1044,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>13.4</v>
+        <v>18.1</v>
       </c>
       <c r="C17">
-        <v>14.3</v>
+        <v>21.3</v>
       </c>
       <c r="D17">
-        <v>15.4</v>
+        <v>25.2</v>
       </c>
       <c r="E17">
-        <v>16.6</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>17.9</v>
+        <v>35.3</v>
       </c>
       <c r="G17">
-        <v>19.4</v>
+        <v>41.2</v>
       </c>
       <c r="H17">
-        <v>20.8</v>
+        <v>47.3</v>
       </c>
       <c r="I17">
-        <v>22.1</v>
+        <v>53.4</v>
       </c>
       <c r="J17">
-        <v>23.3</v>
+        <v>59.4</v>
       </c>
       <c r="K17">
-        <v>24.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L17">
-        <v>25.1</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1082,37 +1082,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
       <c r="C18">
-        <v>18.6</v>
+        <v>20.9</v>
       </c>
       <c r="D18">
-        <v>19.2</v>
+        <v>23.2</v>
       </c>
       <c r="E18">
-        <v>20.1</v>
+        <v>26.2</v>
       </c>
       <c r="F18">
-        <v>21.3</v>
+        <v>29.7</v>
       </c>
       <c r="G18">
-        <v>22.8</v>
+        <v>33.7</v>
       </c>
       <c r="H18">
-        <v>24.2</v>
+        <v>37.8</v>
       </c>
       <c r="I18">
-        <v>25.5</v>
+        <v>42.2</v>
       </c>
       <c r="J18">
-        <v>26.6</v>
+        <v>46.6</v>
       </c>
       <c r="K18">
-        <v>27.4</v>
+        <v>50.9</v>
       </c>
       <c r="L18">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1120,37 +1120,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>20.1</v>
+        <v>19.2</v>
       </c>
       <c r="C19">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="D19">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="E19">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="F19">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="G19">
-        <v>24.2</v>
+        <v>22.5</v>
       </c>
       <c r="H19">
-        <v>25.9</v>
+        <v>23.2</v>
       </c>
       <c r="I19">
-        <v>27.7</v>
+        <v>23.9</v>
       </c>
       <c r="J19">
-        <v>29.4</v>
+        <v>24.6</v>
       </c>
       <c r="K19">
-        <v>30.8</v>
+        <v>25.3</v>
       </c>
       <c r="L19">
-        <v>31.9</v>
+        <v>26.2</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
@@ -436,37 +436,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="C1" s="1">
-        <v>46106</v>
+        <v>46141</v>
       </c>
       <c r="D1" s="1">
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="E1" s="1">
-        <v>46120</v>
+        <v>46155</v>
       </c>
       <c r="F1" s="1">
-        <v>46127</v>
+        <v>46162</v>
       </c>
       <c r="G1" s="1">
-        <v>46134</v>
+        <v>46169</v>
       </c>
       <c r="H1" s="1">
-        <v>46141</v>
+        <v>46176</v>
       </c>
       <c r="I1" s="1">
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="J1" s="1">
-        <v>46155</v>
+        <v>46190</v>
       </c>
       <c r="K1" s="1">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="L1" s="1">
-        <v>46169</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -474,37 +474,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>24.7</v>
+        <v>48.1</v>
       </c>
       <c r="C2">
-        <v>28.6</v>
+        <v>52.8</v>
       </c>
       <c r="D2">
-        <v>33.2</v>
+        <v>56.8</v>
       </c>
       <c r="E2">
-        <v>38.5</v>
+        <v>59.9</v>
       </c>
       <c r="F2">
-        <v>44.3</v>
+        <v>62</v>
       </c>
       <c r="G2">
-        <v>50.5</v>
+        <v>62.9</v>
       </c>
       <c r="H2">
-        <v>56.8</v>
+        <v>62.6</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J2">
-        <v>69</v>
+        <v>58.4</v>
       </c>
       <c r="K2">
-        <v>74.3</v>
+        <v>55</v>
       </c>
       <c r="L2">
-        <v>78.90000000000001</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -512,37 +512,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>33.7</v>
+        <v>57.6</v>
       </c>
       <c r="C3">
-        <v>38.5</v>
+        <v>61.2</v>
       </c>
       <c r="D3">
-        <v>43.8</v>
+        <v>63.8</v>
       </c>
       <c r="E3">
-        <v>49.7</v>
+        <v>65.3</v>
       </c>
       <c r="F3">
-        <v>55.9</v>
+        <v>65.5</v>
       </c>
       <c r="G3">
-        <v>62.3</v>
+        <v>64.3</v>
       </c>
       <c r="H3">
-        <v>68.7</v>
+        <v>61.8</v>
       </c>
       <c r="I3">
-        <v>74.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="J3">
-        <v>80.7</v>
+        <v>53.4</v>
       </c>
       <c r="K3">
-        <v>85.7</v>
+        <v>48.1</v>
       </c>
       <c r="L3">
-        <v>89.8</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -550,37 +550,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>19.1</v>
+        <v>37.3</v>
       </c>
       <c r="C4">
-        <v>22.8</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>26.7</v>
+        <v>42.2</v>
       </c>
       <c r="E4">
-        <v>30.9</v>
+        <v>43.5</v>
       </c>
       <c r="F4">
-        <v>35.2</v>
+        <v>44.1</v>
       </c>
       <c r="G4">
-        <v>39.7</v>
+        <v>43.8</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>42.7</v>
       </c>
       <c r="I4">
-        <v>48.2</v>
+        <v>41</v>
       </c>
       <c r="J4">
-        <v>52</v>
+        <v>38.8</v>
       </c>
       <c r="K4">
-        <v>55.4</v>
+        <v>36.4</v>
       </c>
       <c r="L4">
-        <v>58.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -588,37 +588,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>18.8</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>22.1</v>
+        <v>50.6</v>
       </c>
       <c r="D5">
-        <v>25.9</v>
+        <v>55.7</v>
       </c>
       <c r="E5">
-        <v>29.9</v>
+        <v>59.9</v>
       </c>
       <c r="F5">
-        <v>34.2</v>
+        <v>62.9</v>
       </c>
       <c r="G5">
-        <v>38.5</v>
+        <v>64.5</v>
       </c>
       <c r="H5">
-        <v>42.8</v>
+        <v>64.5</v>
       </c>
       <c r="I5">
-        <v>46.9</v>
+        <v>63.1</v>
       </c>
       <c r="J5">
-        <v>50.6</v>
+        <v>60.3</v>
       </c>
       <c r="K5">
-        <v>53.8</v>
+        <v>56.4</v>
       </c>
       <c r="L5">
-        <v>56.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -626,37 +626,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>31.8</v>
+        <v>57.2</v>
       </c>
       <c r="C6">
-        <v>37.6</v>
+        <v>60.5</v>
       </c>
       <c r="D6">
-        <v>44.8</v>
+        <v>62.4</v>
       </c>
       <c r="E6">
-        <v>53.3</v>
+        <v>62.6</v>
       </c>
       <c r="F6">
-        <v>63</v>
+        <v>61.1</v>
       </c>
       <c r="G6">
-        <v>73.5</v>
+        <v>57.9</v>
       </c>
       <c r="H6">
-        <v>84.5</v>
+        <v>53.1</v>
       </c>
       <c r="I6">
-        <v>95.5</v>
+        <v>47</v>
       </c>
       <c r="J6">
-        <v>106.1</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>115.8</v>
+        <v>32.6</v>
       </c>
       <c r="L6">
-        <v>124.1</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -664,37 +664,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>34.2</v>
+        <v>56.5</v>
       </c>
       <c r="C7">
-        <v>39.4</v>
+        <v>59.6</v>
       </c>
       <c r="D7">
-        <v>45.4</v>
+        <v>61.5</v>
       </c>
       <c r="E7">
-        <v>52.3</v>
+        <v>62.1</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>61.2</v>
       </c>
       <c r="G7">
-        <v>68.2</v>
+        <v>59</v>
       </c>
       <c r="H7">
-        <v>76.7</v>
+        <v>55.4</v>
       </c>
       <c r="I7">
-        <v>85.2</v>
+        <v>50.6</v>
       </c>
       <c r="J7">
-        <v>93.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="K7">
-        <v>100.7</v>
+        <v>38.9</v>
       </c>
       <c r="L7">
-        <v>106.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -702,37 +702,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>18.3</v>
+        <v>46.4</v>
       </c>
       <c r="C8">
-        <v>24.1</v>
+        <v>51.3</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>55.2</v>
       </c>
       <c r="E8">
-        <v>38.9</v>
+        <v>57.8</v>
       </c>
       <c r="F8">
-        <v>47.8</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>57.2</v>
+        <v>58.6</v>
       </c>
       <c r="H8">
-        <v>66.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="I8">
-        <v>76.40000000000001</v>
+        <v>53.7</v>
       </c>
       <c r="J8">
-        <v>85.40000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="K8">
-        <v>93.40000000000001</v>
+        <v>44.7</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -740,37 +740,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>29.7</v>
+        <v>50.2</v>
       </c>
       <c r="C9">
-        <v>34.8</v>
+        <v>52.8</v>
       </c>
       <c r="D9">
-        <v>40.7</v>
+        <v>54.4</v>
       </c>
       <c r="E9">
-        <v>47.4</v>
+        <v>54.9</v>
       </c>
       <c r="F9">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>62.7</v>
+        <v>52</v>
       </c>
       <c r="H9">
-        <v>70.8</v>
+        <v>48.9</v>
       </c>
       <c r="I9">
-        <v>78.7</v>
+        <v>45</v>
       </c>
       <c r="J9">
-        <v>86.2</v>
+        <v>40.4</v>
       </c>
       <c r="K9">
-        <v>92.90000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="L9">
-        <v>98.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -778,37 +778,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>16.8</v>
+        <v>34.9</v>
       </c>
       <c r="C10">
-        <v>18.7</v>
+        <v>39.5</v>
       </c>
       <c r="D10">
-        <v>20.9</v>
+        <v>44</v>
       </c>
       <c r="E10">
-        <v>23.3</v>
+        <v>48.3</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>51.9</v>
       </c>
       <c r="G10">
-        <v>28.9</v>
+        <v>54.8</v>
       </c>
       <c r="H10">
-        <v>31.9</v>
+        <v>56.7</v>
       </c>
       <c r="I10">
-        <v>35</v>
+        <v>57.6</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>57.5</v>
       </c>
       <c r="K10">
-        <v>40.9</v>
+        <v>56.4</v>
       </c>
       <c r="L10">
-        <v>43.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -816,37 +816,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>20.2</v>
+        <v>54</v>
       </c>
       <c r="C11">
-        <v>26.9</v>
+        <v>60.2</v>
       </c>
       <c r="D11">
-        <v>35.1</v>
+        <v>65.2</v>
       </c>
       <c r="E11">
-        <v>44.6</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F11">
-        <v>55.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G11">
-        <v>66.7</v>
+        <v>71.2</v>
       </c>
       <c r="H11">
-        <v>78.5</v>
+        <v>69.7</v>
       </c>
       <c r="I11">
-        <v>90.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J11">
-        <v>101.3</v>
+        <v>62.2</v>
       </c>
       <c r="K11">
-        <v>111.3</v>
+        <v>56.9</v>
       </c>
       <c r="L11">
-        <v>119.7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -854,37 +854,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>26.2</v>
+        <v>45.9</v>
       </c>
       <c r="C12">
-        <v>29.9</v>
+        <v>49.5</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>52.5</v>
       </c>
       <c r="E12">
-        <v>38.4</v>
+        <v>54.8</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>56.2</v>
       </c>
       <c r="G12">
-        <v>47.9</v>
+        <v>56.6</v>
       </c>
       <c r="H12">
-        <v>52.9</v>
+        <v>56</v>
       </c>
       <c r="I12">
-        <v>57.7</v>
+        <v>54.5</v>
       </c>
       <c r="J12">
-        <v>62.2</v>
+        <v>52.1</v>
       </c>
       <c r="K12">
-        <v>66.2</v>
+        <v>49.2</v>
       </c>
       <c r="L12">
-        <v>69.59999999999999</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -892,37 +892,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>39.3</v>
+        <v>60.9</v>
       </c>
       <c r="C13">
-        <v>43.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D13">
-        <v>48.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E13">
-        <v>54.1</v>
+        <v>69</v>
       </c>
       <c r="F13">
-        <v>59.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G13">
-        <v>64.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="H13">
-        <v>70.2</v>
+        <v>68.7</v>
       </c>
       <c r="I13">
-        <v>75.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J13">
-        <v>79.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="K13">
-        <v>83.3</v>
+        <v>60.3</v>
       </c>
       <c r="L13">
-        <v>86.3</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -930,37 +930,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>26.7</v>
+        <v>48.5</v>
       </c>
       <c r="C14">
-        <v>29.8</v>
+        <v>53.5</v>
       </c>
       <c r="D14">
-        <v>33.4</v>
+        <v>58.3</v>
       </c>
       <c r="E14">
-        <v>37.5</v>
+        <v>62.6</v>
       </c>
       <c r="F14">
-        <v>41.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G14">
-        <v>46.7</v>
+        <v>69.3</v>
       </c>
       <c r="H14">
-        <v>51.8</v>
+        <v>71.2</v>
       </c>
       <c r="I14">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="J14">
-        <v>62.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K14">
-        <v>67.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L14">
-        <v>71.8</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -968,37 +968,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>32.4</v>
+        <v>53.4</v>
       </c>
       <c r="C15">
-        <v>37.2</v>
+        <v>56.3</v>
       </c>
       <c r="D15">
-        <v>42.8</v>
+        <v>58</v>
       </c>
       <c r="E15">
-        <v>49.2</v>
+        <v>58.6</v>
       </c>
       <c r="F15">
-        <v>56.2</v>
+        <v>57.7</v>
       </c>
       <c r="G15">
-        <v>63.8</v>
+        <v>55.6</v>
       </c>
       <c r="H15">
-        <v>71.59999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="I15">
-        <v>79.5</v>
+        <v>47.8</v>
       </c>
       <c r="J15">
-        <v>86.90000000000001</v>
+        <v>42.6</v>
       </c>
       <c r="K15">
-        <v>93.7</v>
+        <v>37</v>
       </c>
       <c r="L15">
-        <v>99.40000000000001</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1006,37 +1006,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>15.6</v>
+        <v>41</v>
       </c>
       <c r="C16">
-        <v>19</v>
+        <v>47.2</v>
       </c>
       <c r="D16">
-        <v>23.2</v>
+        <v>53.1</v>
       </c>
       <c r="E16">
-        <v>28.1</v>
+        <v>58.3</v>
       </c>
       <c r="F16">
-        <v>33.5</v>
+        <v>62.7</v>
       </c>
       <c r="G16">
-        <v>39.4</v>
+        <v>65.8</v>
       </c>
       <c r="H16">
-        <v>45.4</v>
+        <v>67.7</v>
       </c>
       <c r="I16">
-        <v>51.4</v>
+        <v>68.2</v>
       </c>
       <c r="J16">
-        <v>57</v>
+        <v>67.3</v>
       </c>
       <c r="K16">
-        <v>62.1</v>
+        <v>65.3</v>
       </c>
       <c r="L16">
-        <v>66.5</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1044,37 +1044,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>18.1</v>
+        <v>43</v>
       </c>
       <c r="C17">
-        <v>21.3</v>
+        <v>49.5</v>
       </c>
       <c r="D17">
-        <v>25.2</v>
+        <v>55.8</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>61.6</v>
       </c>
       <c r="F17">
-        <v>35.3</v>
+        <v>66.7</v>
       </c>
       <c r="G17">
-        <v>41.2</v>
+        <v>70.8</v>
       </c>
       <c r="H17">
-        <v>47.3</v>
+        <v>73.7</v>
       </c>
       <c r="I17">
-        <v>53.4</v>
+        <v>75.2</v>
       </c>
       <c r="J17">
-        <v>59.4</v>
+        <v>75.5</v>
       </c>
       <c r="K17">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="L17">
-        <v>69.8</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1082,37 +1082,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>19.2</v>
+        <v>47.2</v>
       </c>
       <c r="C18">
-        <v>20.9</v>
+        <v>54.9</v>
       </c>
       <c r="D18">
-        <v>23.2</v>
+        <v>62.4</v>
       </c>
       <c r="E18">
-        <v>26.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F18">
-        <v>29.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G18">
-        <v>33.7</v>
+        <v>80</v>
       </c>
       <c r="H18">
-        <v>37.8</v>
+        <v>83</v>
       </c>
       <c r="I18">
-        <v>42.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J18">
-        <v>46.6</v>
+        <v>83.3</v>
       </c>
       <c r="K18">
-        <v>50.9</v>
+        <v>80.8</v>
       </c>
       <c r="L18">
-        <v>55</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1120,37 +1120,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>19.2</v>
+        <v>39.3</v>
       </c>
       <c r="C19">
-        <v>19.6</v>
+        <v>46.3</v>
       </c>
       <c r="D19">
-        <v>20.2</v>
+        <v>53.8</v>
       </c>
       <c r="E19">
-        <v>20.9</v>
+        <v>61.5</v>
       </c>
       <c r="F19">
-        <v>21.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G19">
-        <v>22.5</v>
+        <v>75.8</v>
       </c>
       <c r="H19">
-        <v>23.2</v>
+        <v>81.8</v>
       </c>
       <c r="I19">
-        <v>23.9</v>
+        <v>86.5</v>
       </c>
       <c r="J19">
-        <v>24.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K19">
-        <v>25.3</v>
+        <v>91</v>
       </c>
       <c r="L19">
-        <v>26.2</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
@@ -436,37 +436,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="C1" s="1">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="D1" s="1">
-        <v>46148</v>
+        <v>46176</v>
       </c>
       <c r="E1" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="F1" s="1">
-        <v>46162</v>
+        <v>46190</v>
       </c>
       <c r="G1" s="1">
-        <v>46169</v>
+        <v>46197</v>
       </c>
       <c r="H1" s="1">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="I1" s="1">
-        <v>46183</v>
+        <v>46211</v>
       </c>
       <c r="J1" s="1">
-        <v>46190</v>
+        <v>46218</v>
       </c>
       <c r="K1" s="1">
-        <v>46197</v>
+        <v>46225</v>
       </c>
       <c r="L1" s="1">
-        <v>46204</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -474,37 +474,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>48.1</v>
+        <v>62.2</v>
       </c>
       <c r="C2">
-        <v>52.8</v>
+        <v>63.3</v>
       </c>
       <c r="D2">
-        <v>56.8</v>
+        <v>63.1</v>
       </c>
       <c r="E2">
-        <v>59.9</v>
+        <v>61.9</v>
       </c>
       <c r="F2">
-        <v>62</v>
+        <v>59.6</v>
       </c>
       <c r="G2">
-        <v>62.9</v>
+        <v>56.5</v>
       </c>
       <c r="H2">
-        <v>62.6</v>
+        <v>52.9</v>
       </c>
       <c r="I2">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J2">
-        <v>58.4</v>
+        <v>45.2</v>
       </c>
       <c r="K2">
-        <v>55</v>
+        <v>41.8</v>
       </c>
       <c r="L2">
-        <v>50.9</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -512,37 +512,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>57.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C3">
-        <v>61.2</v>
+        <v>67.8</v>
       </c>
       <c r="D3">
+        <v>67.2</v>
+      </c>
+      <c r="E3">
+        <v>65.8</v>
+      </c>
+      <c r="F3">
         <v>63.8</v>
       </c>
-      <c r="E3">
-        <v>65.3</v>
-      </c>
-      <c r="F3">
-        <v>65.5</v>
-      </c>
       <c r="G3">
-        <v>64.3</v>
+        <v>61.4</v>
       </c>
       <c r="H3">
-        <v>61.8</v>
+        <v>58.9</v>
       </c>
       <c r="I3">
-        <v>58</v>
+        <v>56.5</v>
       </c>
       <c r="J3">
-        <v>53.4</v>
+        <v>54.5</v>
       </c>
       <c r="K3">
-        <v>48.1</v>
+        <v>52.8</v>
       </c>
       <c r="L3">
-        <v>42.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -550,37 +550,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>37.3</v>
+        <v>52.6</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>56.5</v>
       </c>
       <c r="D4">
-        <v>42.2</v>
+        <v>60.3</v>
       </c>
       <c r="E4">
-        <v>43.5</v>
+        <v>64</v>
       </c>
       <c r="F4">
-        <v>44.1</v>
+        <v>67.5</v>
       </c>
       <c r="G4">
-        <v>43.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H4">
-        <v>42.7</v>
+        <v>73.8</v>
       </c>
       <c r="I4">
-        <v>41</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J4">
-        <v>38.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K4">
-        <v>36.4</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L4">
-        <v>33.9</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -588,37 +588,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>45</v>
+        <v>63.8</v>
       </c>
       <c r="C5">
-        <v>50.6</v>
+        <v>65.7</v>
       </c>
       <c r="D5">
-        <v>55.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E5">
-        <v>59.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F5">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="G5">
-        <v>64.5</v>
+        <v>58.5</v>
       </c>
       <c r="H5">
-        <v>64.5</v>
+        <v>53.7</v>
       </c>
       <c r="I5">
-        <v>63.1</v>
+        <v>48.4</v>
       </c>
       <c r="J5">
-        <v>60.3</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>56.4</v>
+        <v>37.9</v>
       </c>
       <c r="L5">
-        <v>51.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -626,37 +626,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>57.2</v>
+        <v>63.8</v>
       </c>
       <c r="C6">
-        <v>60.5</v>
+        <v>62.3</v>
       </c>
       <c r="D6">
-        <v>62.4</v>
+        <v>59.8</v>
       </c>
       <c r="E6">
-        <v>62.6</v>
+        <v>56.4</v>
       </c>
       <c r="F6">
-        <v>61.1</v>
+        <v>52.5</v>
       </c>
       <c r="G6">
-        <v>57.9</v>
+        <v>48.5</v>
       </c>
       <c r="H6">
-        <v>53.1</v>
+        <v>44.7</v>
       </c>
       <c r="I6">
-        <v>47</v>
+        <v>41.5</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>39.1</v>
       </c>
       <c r="K6">
-        <v>32.6</v>
+        <v>37.8</v>
       </c>
       <c r="L6">
-        <v>25.4</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -664,37 +664,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>56.5</v>
+        <v>66.5</v>
       </c>
       <c r="C7">
-        <v>59.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D7">
-        <v>61.5</v>
+        <v>65.8</v>
       </c>
       <c r="E7">
-        <v>62.1</v>
+        <v>64</v>
       </c>
       <c r="F7">
-        <v>61.2</v>
+        <v>61.6</v>
       </c>
       <c r="G7">
-        <v>59</v>
+        <v>58.6</v>
       </c>
       <c r="H7">
         <v>55.4</v>
       </c>
       <c r="I7">
-        <v>50.6</v>
+        <v>52.3</v>
       </c>
       <c r="J7">
+        <v>49.4</v>
+      </c>
+      <c r="K7">
+        <v>46.9</v>
+      </c>
+      <c r="L7">
         <v>45</v>
-      </c>
-      <c r="K7">
-        <v>38.9</v>
-      </c>
-      <c r="L7">
-        <v>32.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -702,37 +702,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>46.4</v>
+        <v>59.4</v>
       </c>
       <c r="C8">
-        <v>51.3</v>
+        <v>59.4</v>
       </c>
       <c r="D8">
+        <v>57.9</v>
+      </c>
+      <c r="E8">
         <v>55.2</v>
       </c>
-      <c r="E8">
-        <v>57.8</v>
-      </c>
       <c r="F8">
-        <v>59</v>
+        <v>51.6</v>
       </c>
       <c r="G8">
-        <v>58.6</v>
+        <v>47.2</v>
       </c>
       <c r="H8">
-        <v>56.8</v>
+        <v>42.7</v>
       </c>
       <c r="I8">
-        <v>53.7</v>
+        <v>38.2</v>
       </c>
       <c r="J8">
-        <v>49.5</v>
+        <v>34.1</v>
       </c>
       <c r="K8">
-        <v>44.7</v>
+        <v>30.8</v>
       </c>
       <c r="L8">
-        <v>39.5</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -740,37 +740,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>50.2</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
       <c r="D9">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="E9">
-        <v>54.9</v>
+        <v>52.1</v>
       </c>
       <c r="F9">
-        <v>54</v>
+        <v>49.1</v>
       </c>
       <c r="G9">
-        <v>52</v>
+        <v>45.8</v>
       </c>
       <c r="H9">
-        <v>48.9</v>
+        <v>42.5</v>
       </c>
       <c r="I9">
-        <v>45</v>
+        <v>39.4</v>
       </c>
       <c r="J9">
-        <v>40.4</v>
+        <v>36.7</v>
       </c>
       <c r="K9">
-        <v>35.7</v>
+        <v>34.6</v>
       </c>
       <c r="L9">
-        <v>31</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -778,37 +778,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>34.9</v>
+        <v>50.3</v>
       </c>
       <c r="C10">
-        <v>39.5</v>
+        <v>52.3</v>
       </c>
       <c r="D10">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E10">
+        <v>52.6</v>
+      </c>
+      <c r="F10">
+        <v>51</v>
+      </c>
+      <c r="G10">
         <v>48.3</v>
       </c>
-      <c r="F10">
-        <v>51.9</v>
-      </c>
-      <c r="G10">
-        <v>54.8</v>
-      </c>
       <c r="H10">
-        <v>56.7</v>
+        <v>44.7</v>
       </c>
       <c r="I10">
-        <v>57.6</v>
+        <v>40.7</v>
       </c>
       <c r="J10">
-        <v>57.5</v>
+        <v>36.4</v>
       </c>
       <c r="K10">
-        <v>56.4</v>
+        <v>32.3</v>
       </c>
       <c r="L10">
-        <v>54.5</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -816,37 +816,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>54</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="C11">
-        <v>60.2</v>
+        <v>69.5</v>
       </c>
       <c r="D11">
-        <v>65.2</v>
+        <v>67.7</v>
       </c>
       <c r="E11">
-        <v>68.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="F11">
-        <v>70.90000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="G11">
-        <v>71.2</v>
+        <v>54.3</v>
       </c>
       <c r="H11">
-        <v>69.7</v>
+        <v>48.5</v>
       </c>
       <c r="I11">
-        <v>66.59999999999999</v>
+        <v>42.8</v>
       </c>
       <c r="J11">
-        <v>62.2</v>
+        <v>37.6</v>
       </c>
       <c r="K11">
-        <v>56.9</v>
+        <v>33.4</v>
       </c>
       <c r="L11">
-        <v>51</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -854,37 +854,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>45.9</v>
+        <v>60</v>
       </c>
       <c r="C12">
-        <v>49.5</v>
+        <v>62.3</v>
       </c>
       <c r="D12">
-        <v>52.5</v>
+        <v>64</v>
       </c>
       <c r="E12">
-        <v>54.8</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>56.2</v>
+        <v>65.5</v>
       </c>
       <c r="G12">
-        <v>56.6</v>
+        <v>65.3</v>
       </c>
       <c r="H12">
-        <v>56</v>
+        <v>64.8</v>
       </c>
       <c r="I12">
-        <v>54.5</v>
+        <v>63.8</v>
       </c>
       <c r="J12">
-        <v>52.1</v>
+        <v>62.7</v>
       </c>
       <c r="K12">
-        <v>49.2</v>
+        <v>61.4</v>
       </c>
       <c r="L12">
-        <v>45.9</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -892,37 +892,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>60.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C13">
-        <v>64.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="D13">
-        <v>67.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="E13">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="F13">
-        <v>69.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G13">
-        <v>69.8</v>
+        <v>62.1</v>
       </c>
       <c r="H13">
-        <v>68.7</v>
+        <v>59.9</v>
       </c>
       <c r="I13">
-        <v>66.59999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="J13">
-        <v>63.8</v>
+        <v>56.1</v>
       </c>
       <c r="K13">
-        <v>60.3</v>
+        <v>54.9</v>
       </c>
       <c r="L13">
-        <v>56.4</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -930,37 +930,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>48.5</v>
+        <v>62.6</v>
       </c>
       <c r="C14">
-        <v>53.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D14">
-        <v>58.3</v>
+        <v>64.5</v>
       </c>
       <c r="E14">
-        <v>62.6</v>
+        <v>63.8</v>
       </c>
       <c r="F14">
-        <v>66.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="G14">
-        <v>69.3</v>
+        <v>59.4</v>
       </c>
       <c r="H14">
-        <v>71.2</v>
+        <v>56.1</v>
       </c>
       <c r="I14">
-        <v>72</v>
+        <v>52.4</v>
       </c>
       <c r="J14">
-        <v>71.59999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="K14">
-        <v>70.09999999999999</v>
+        <v>45.2</v>
       </c>
       <c r="L14">
-        <v>67.59999999999999</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -968,37 +968,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>53.4</v>
+        <v>62.6</v>
       </c>
       <c r="C15">
-        <v>56.3</v>
+        <v>62.9</v>
       </c>
       <c r="D15">
-        <v>58</v>
+        <v>62.4</v>
       </c>
       <c r="E15">
-        <v>58.6</v>
+        <v>61.2</v>
       </c>
       <c r="F15">
-        <v>57.7</v>
+        <v>59.5</v>
       </c>
       <c r="G15">
-        <v>55.6</v>
+        <v>57.5</v>
       </c>
       <c r="H15">
-        <v>52.2</v>
+        <v>55.4</v>
       </c>
       <c r="I15">
-        <v>47.8</v>
+        <v>53.5</v>
       </c>
       <c r="J15">
-        <v>42.6</v>
+        <v>51.8</v>
       </c>
       <c r="K15">
-        <v>37</v>
+        <v>50.6</v>
       </c>
       <c r="L15">
-        <v>31.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1006,37 +1006,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>41</v>
+        <v>60.6</v>
       </c>
       <c r="C16">
-        <v>47.2</v>
+        <v>62.7</v>
       </c>
       <c r="D16">
-        <v>53.1</v>
+        <v>63.1</v>
       </c>
       <c r="E16">
-        <v>58.3</v>
+        <v>61.9</v>
       </c>
       <c r="F16">
-        <v>62.7</v>
+        <v>59.3</v>
       </c>
       <c r="G16">
-        <v>65.8</v>
+        <v>55.3</v>
       </c>
       <c r="H16">
-        <v>67.7</v>
+        <v>50.4</v>
       </c>
       <c r="I16">
-        <v>68.2</v>
+        <v>44.9</v>
       </c>
       <c r="J16">
-        <v>67.3</v>
+        <v>39.2</v>
       </c>
       <c r="K16">
-        <v>65.3</v>
+        <v>33.8</v>
       </c>
       <c r="L16">
-        <v>62.3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1044,37 +1044,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>43</v>
+        <v>62.1</v>
       </c>
       <c r="C17">
-        <v>49.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D17">
-        <v>55.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E17">
-        <v>61.6</v>
+        <v>63.2</v>
       </c>
       <c r="F17">
-        <v>66.7</v>
+        <v>60.5</v>
       </c>
       <c r="G17">
-        <v>70.8</v>
+        <v>56.5</v>
       </c>
       <c r="H17">
-        <v>73.7</v>
+        <v>51.4</v>
       </c>
       <c r="I17">
-        <v>75.2</v>
+        <v>45.8</v>
       </c>
       <c r="J17">
-        <v>75.5</v>
+        <v>39.9</v>
       </c>
       <c r="K17">
-        <v>74.40000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="L17">
-        <v>72.09999999999999</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1082,37 +1082,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>47.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C18">
-        <v>54.9</v>
+        <v>73.3</v>
       </c>
       <c r="D18">
-        <v>62.4</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E18">
-        <v>69.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="F18">
-        <v>75.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="G18">
-        <v>80</v>
+        <v>61.7</v>
       </c>
       <c r="H18">
-        <v>83</v>
+        <v>54.3</v>
       </c>
       <c r="I18">
-        <v>84.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="J18">
-        <v>83.3</v>
+        <v>37</v>
       </c>
       <c r="K18">
-        <v>80.8</v>
+        <v>28.5</v>
       </c>
       <c r="L18">
-        <v>76.59999999999999</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1120,37 +1120,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>39.3</v>
+        <v>59.4</v>
       </c>
       <c r="C19">
-        <v>46.3</v>
+        <v>61.4</v>
       </c>
       <c r="D19">
-        <v>53.8</v>
+        <v>61.4</v>
       </c>
       <c r="E19">
-        <v>61.5</v>
+        <v>59.4</v>
       </c>
       <c r="F19">
-        <v>68.90000000000001</v>
+        <v>55.3</v>
       </c>
       <c r="G19">
-        <v>75.8</v>
+        <v>49.3</v>
       </c>
       <c r="H19">
-        <v>81.8</v>
+        <v>41.8</v>
       </c>
       <c r="I19">
-        <v>86.5</v>
+        <v>33.1</v>
       </c>
       <c r="J19">
-        <v>89.59999999999999</v>
+        <v>24</v>
       </c>
       <c r="K19">
-        <v>91</v>
+        <v>15.2</v>
       </c>
       <c r="L19">
-        <v>90.59999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
@@ -436,37 +436,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="C1" s="1">
-        <v>46169</v>
+        <v>46204</v>
       </c>
       <c r="D1" s="1">
-        <v>46176</v>
+        <v>46211</v>
       </c>
       <c r="E1" s="1">
-        <v>46183</v>
+        <v>46218</v>
       </c>
       <c r="F1" s="1">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="G1" s="1">
-        <v>46197</v>
+        <v>46232</v>
       </c>
       <c r="H1" s="1">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="I1" s="1">
-        <v>46211</v>
+        <v>46246</v>
       </c>
       <c r="J1" s="1">
-        <v>46218</v>
+        <v>46253</v>
       </c>
       <c r="K1" s="1">
-        <v>46225</v>
+        <v>46260</v>
       </c>
       <c r="L1" s="1">
-        <v>46232</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -474,37 +474,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>62.2</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>63.3</v>
+        <v>58.5</v>
       </c>
       <c r="D2">
-        <v>63.1</v>
+        <v>57.2</v>
       </c>
       <c r="E2">
-        <v>61.9</v>
+        <v>56.5</v>
       </c>
       <c r="F2">
-        <v>59.6</v>
+        <v>56.4</v>
       </c>
       <c r="G2">
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="H2">
-        <v>52.9</v>
+        <v>58.4</v>
       </c>
       <c r="I2">
-        <v>49</v>
+        <v>60.3</v>
       </c>
       <c r="J2">
-        <v>45.2</v>
+        <v>62.6</v>
       </c>
       <c r="K2">
-        <v>41.8</v>
+        <v>65</v>
       </c>
       <c r="L2">
-        <v>38.9</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -512,37 +512,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>67.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="C3">
-        <v>67.8</v>
+        <v>61.6</v>
       </c>
       <c r="D3">
-        <v>67.2</v>
+        <v>59.8</v>
       </c>
       <c r="E3">
-        <v>65.8</v>
+        <v>58.2</v>
       </c>
       <c r="F3">
-        <v>63.8</v>
+        <v>56.9</v>
       </c>
       <c r="G3">
-        <v>61.4</v>
+        <v>56</v>
       </c>
       <c r="H3">
-        <v>58.9</v>
+        <v>55.5</v>
       </c>
       <c r="I3">
-        <v>56.5</v>
+        <v>55.1</v>
       </c>
       <c r="J3">
-        <v>54.5</v>
+        <v>54.9</v>
       </c>
       <c r="K3">
-        <v>52.8</v>
+        <v>54.7</v>
       </c>
       <c r="L3">
-        <v>51.8</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -550,37 +550,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>52.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C4">
-        <v>56.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D4">
-        <v>60.3</v>
+        <v>71.2</v>
       </c>
       <c r="E4">
-        <v>64</v>
+        <v>72.3</v>
       </c>
       <c r="F4">
-        <v>67.5</v>
+        <v>72.8</v>
       </c>
       <c r="G4">
+        <v>72.7</v>
+      </c>
+      <c r="H4">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="I4">
         <v>70.90000000000001</v>
       </c>
-      <c r="H4">
-        <v>73.8</v>
-      </c>
-      <c r="I4">
-        <v>76.40000000000001</v>
-      </c>
       <c r="J4">
-        <v>78.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K4">
-        <v>79.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="L4">
-        <v>80.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -588,37 +588,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>63.8</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>65.7</v>
+        <v>61.3</v>
       </c>
       <c r="D5">
-        <v>66.09999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="E5">
-        <v>64.90000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="F5">
-        <v>62.3</v>
+        <v>58.3</v>
       </c>
       <c r="G5">
-        <v>58.5</v>
+        <v>58.9</v>
       </c>
       <c r="H5">
-        <v>53.7</v>
+        <v>60.3</v>
       </c>
       <c r="I5">
-        <v>48.4</v>
+        <v>62.5</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>65.3</v>
       </c>
       <c r="K5">
-        <v>37.9</v>
+        <v>68.3</v>
       </c>
       <c r="L5">
-        <v>33.3</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -626,37 +626,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>63.8</v>
+        <v>50.1</v>
       </c>
       <c r="C6">
-        <v>62.3</v>
+        <v>47.6</v>
       </c>
       <c r="D6">
-        <v>59.8</v>
+        <v>46.1</v>
       </c>
       <c r="E6">
-        <v>56.4</v>
+        <v>45.7</v>
       </c>
       <c r="F6">
-        <v>52.5</v>
+        <v>46.7</v>
       </c>
       <c r="G6">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="H6">
-        <v>44.7</v>
+        <v>52.1</v>
       </c>
       <c r="I6">
-        <v>41.5</v>
+        <v>56.1</v>
       </c>
       <c r="J6">
-        <v>39.1</v>
+        <v>60.5</v>
       </c>
       <c r="K6">
-        <v>37.8</v>
+        <v>64.8</v>
       </c>
       <c r="L6">
-        <v>37.4</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -664,37 +664,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>66.5</v>
+        <v>59.6</v>
       </c>
       <c r="C7">
-        <v>66.59999999999999</v>
+        <v>56.9</v>
       </c>
       <c r="D7">
-        <v>65.8</v>
+        <v>54.5</v>
       </c>
       <c r="E7">
-        <v>64</v>
+        <v>52.3</v>
       </c>
       <c r="F7">
-        <v>61.6</v>
+        <v>50.6</v>
       </c>
       <c r="G7">
-        <v>58.6</v>
+        <v>49.5</v>
       </c>
       <c r="H7">
-        <v>55.4</v>
+        <v>49</v>
       </c>
       <c r="I7">
-        <v>52.3</v>
+        <v>48.9</v>
       </c>
       <c r="J7">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="K7">
-        <v>46.9</v>
+        <v>49.7</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -702,37 +702,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>59.4</v>
+        <v>52</v>
       </c>
       <c r="C8">
-        <v>59.4</v>
+        <v>49.8</v>
       </c>
       <c r="D8">
-        <v>57.9</v>
+        <v>48</v>
       </c>
       <c r="E8">
-        <v>55.2</v>
+        <v>47</v>
       </c>
       <c r="F8">
-        <v>51.6</v>
+        <v>46.9</v>
       </c>
       <c r="G8">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="H8">
-        <v>42.7</v>
+        <v>49.2</v>
       </c>
       <c r="I8">
-        <v>38.2</v>
+        <v>51.3</v>
       </c>
       <c r="J8">
-        <v>34.1</v>
+        <v>53.8</v>
       </c>
       <c r="K8">
-        <v>30.8</v>
+        <v>56.3</v>
       </c>
       <c r="L8">
-        <v>28.4</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -740,37 +740,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>57</v>
+        <v>47.3</v>
       </c>
       <c r="C9">
-        <v>56.2</v>
+        <v>44.9</v>
       </c>
       <c r="D9">
-        <v>54.5</v>
+        <v>42.8</v>
       </c>
       <c r="E9">
-        <v>52.1</v>
+        <v>41.3</v>
       </c>
       <c r="F9">
-        <v>49.1</v>
+        <v>40.4</v>
       </c>
       <c r="G9">
-        <v>45.8</v>
+        <v>40.3</v>
       </c>
       <c r="H9">
-        <v>42.5</v>
+        <v>40.8</v>
       </c>
       <c r="I9">
-        <v>39.4</v>
+        <v>41.8</v>
       </c>
       <c r="J9">
-        <v>36.7</v>
+        <v>43.1</v>
       </c>
       <c r="K9">
-        <v>34.6</v>
+        <v>44.6</v>
       </c>
       <c r="L9">
-        <v>33.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -778,37 +778,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>50.3</v>
+        <v>54</v>
       </c>
       <c r="C10">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
       <c r="D10">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="E10">
-        <v>52.6</v>
+        <v>54.4</v>
       </c>
       <c r="F10">
-        <v>51</v>
+        <v>55.6</v>
       </c>
       <c r="G10">
-        <v>48.3</v>
+        <v>57.5</v>
       </c>
       <c r="H10">
-        <v>44.7</v>
+        <v>60.1</v>
       </c>
       <c r="I10">
-        <v>40.7</v>
+        <v>63.2</v>
       </c>
       <c r="J10">
-        <v>36.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K10">
-        <v>32.3</v>
+        <v>70</v>
       </c>
       <c r="L10">
-        <v>28.7</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -816,37 +816,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>69.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="C11">
-        <v>69.5</v>
+        <v>58.4</v>
       </c>
       <c r="D11">
-        <v>67.7</v>
+        <v>57</v>
       </c>
       <c r="E11">
-        <v>64.3</v>
+        <v>56.8</v>
       </c>
       <c r="F11">
-        <v>59.7</v>
+        <v>57.9</v>
       </c>
       <c r="G11">
-        <v>54.3</v>
+        <v>60.4</v>
       </c>
       <c r="H11">
-        <v>48.5</v>
+        <v>64.2</v>
       </c>
       <c r="I11">
-        <v>42.8</v>
+        <v>68.8</v>
       </c>
       <c r="J11">
-        <v>37.6</v>
+        <v>73.8</v>
       </c>
       <c r="K11">
-        <v>33.4</v>
+        <v>78.8</v>
       </c>
       <c r="L11">
-        <v>30.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -854,37 +854,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>60</v>
+        <v>63.9</v>
       </c>
       <c r="C12">
-        <v>62.3</v>
+        <v>63.6</v>
       </c>
       <c r="D12">
-        <v>64</v>
+        <v>63.3</v>
       </c>
       <c r="E12">
-        <v>65</v>
+        <v>63.1</v>
       </c>
       <c r="F12">
-        <v>65.5</v>
+        <v>63.1</v>
       </c>
       <c r="G12">
-        <v>65.3</v>
+        <v>63.4</v>
       </c>
       <c r="H12">
-        <v>64.8</v>
+        <v>63.9</v>
       </c>
       <c r="I12">
-        <v>63.8</v>
+        <v>64.7</v>
       </c>
       <c r="J12">
-        <v>62.7</v>
+        <v>65.7</v>
       </c>
       <c r="K12">
-        <v>61.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L12">
-        <v>60.1</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -892,37 +892,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>68.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="C13">
-        <v>68.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="D13">
-        <v>67.7</v>
+        <v>65.3</v>
       </c>
       <c r="E13">
-        <v>66.2</v>
+        <v>64.7</v>
       </c>
       <c r="F13">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="G13">
-        <v>62.1</v>
+        <v>63.9</v>
       </c>
       <c r="H13">
-        <v>59.9</v>
+        <v>63.7</v>
       </c>
       <c r="I13">
-        <v>57.9</v>
+        <v>63.4</v>
       </c>
       <c r="J13">
-        <v>56.1</v>
+        <v>62.9</v>
       </c>
       <c r="K13">
-        <v>54.9</v>
+        <v>62.2</v>
       </c>
       <c r="L13">
-        <v>54.1</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -930,37 +930,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>62.6</v>
+        <v>65.3</v>
       </c>
       <c r="C14">
-        <v>64.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="D14">
-        <v>64.5</v>
+        <v>65.7</v>
       </c>
       <c r="E14">
-        <v>63.8</v>
+        <v>66.8</v>
       </c>
       <c r="F14">
-        <v>62</v>
+        <v>68.7</v>
       </c>
       <c r="G14">
-        <v>59.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H14">
-        <v>56.1</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I14">
-        <v>52.4</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J14">
-        <v>48.6</v>
+        <v>83.2</v>
       </c>
       <c r="K14">
-        <v>45.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L14">
-        <v>42.3</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -968,37 +968,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>62.6</v>
+        <v>57.1</v>
       </c>
       <c r="C15">
-        <v>62.9</v>
+        <v>55.4</v>
       </c>
       <c r="D15">
-        <v>62.4</v>
+        <v>54</v>
       </c>
       <c r="E15">
-        <v>61.2</v>
+        <v>53.1</v>
       </c>
       <c r="F15">
-        <v>59.5</v>
+        <v>52.8</v>
       </c>
       <c r="G15">
-        <v>57.5</v>
+        <v>53.1</v>
       </c>
       <c r="H15">
-        <v>55.4</v>
+        <v>53.9</v>
       </c>
       <c r="I15">
-        <v>53.5</v>
+        <v>55.2</v>
       </c>
       <c r="J15">
-        <v>51.8</v>
+        <v>56.7</v>
       </c>
       <c r="K15">
-        <v>50.6</v>
+        <v>58.3</v>
       </c>
       <c r="L15">
-        <v>49.8</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1006,37 +1006,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>60.6</v>
+        <v>61.2</v>
       </c>
       <c r="C16">
-        <v>62.7</v>
+        <v>59.8</v>
       </c>
       <c r="D16">
-        <v>63.1</v>
+        <v>58.7</v>
       </c>
       <c r="E16">
-        <v>61.9</v>
+        <v>58.3</v>
       </c>
       <c r="F16">
-        <v>59.3</v>
+        <v>58.6</v>
       </c>
       <c r="G16">
-        <v>55.3</v>
+        <v>59.9</v>
       </c>
       <c r="H16">
-        <v>50.4</v>
+        <v>62.1</v>
       </c>
       <c r="I16">
-        <v>44.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J16">
-        <v>39.2</v>
+        <v>68.5</v>
       </c>
       <c r="K16">
-        <v>33.8</v>
+        <v>72.2</v>
       </c>
       <c r="L16">
-        <v>29</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1044,37 +1044,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>62.1</v>
+        <v>62.9</v>
       </c>
       <c r="C17">
-        <v>64.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="D17">
-        <v>64.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E17">
-        <v>63.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F17">
-        <v>60.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G17">
-        <v>56.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H17">
-        <v>51.4</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I17">
-        <v>45.8</v>
+        <v>84.8</v>
       </c>
       <c r="J17">
-        <v>39.9</v>
+        <v>92</v>
       </c>
       <c r="K17">
-        <v>34.4</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L17">
-        <v>29.5</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1082,37 +1082,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>70.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="C18">
-        <v>73.3</v>
+        <v>59.3</v>
       </c>
       <c r="D18">
-        <v>73.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="E18">
-        <v>71.7</v>
+        <v>48.2</v>
       </c>
       <c r="F18">
-        <v>67.7</v>
+        <v>43.4</v>
       </c>
       <c r="G18">
-        <v>61.7</v>
+        <v>39.9</v>
       </c>
       <c r="H18">
-        <v>54.3</v>
+        <v>37.8</v>
       </c>
       <c r="I18">
-        <v>45.8</v>
+        <v>37.3</v>
       </c>
       <c r="J18">
-        <v>37</v>
+        <v>38.3</v>
       </c>
       <c r="K18">
-        <v>28.5</v>
+        <v>40.5</v>
       </c>
       <c r="L18">
-        <v>20.9</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1120,37 +1120,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
       <c r="C19">
-        <v>61.4</v>
+        <v>57.8</v>
       </c>
       <c r="D19">
-        <v>61.4</v>
+        <v>55.9</v>
       </c>
       <c r="E19">
-        <v>59.4</v>
+        <v>54.4</v>
       </c>
       <c r="F19">
+        <v>53.6</v>
+      </c>
+      <c r="G19">
+        <v>53.9</v>
+      </c>
+      <c r="H19">
         <v>55.3</v>
       </c>
-      <c r="G19">
-        <v>49.3</v>
-      </c>
-      <c r="H19">
-        <v>41.8</v>
-      </c>
       <c r="I19">
-        <v>33.1</v>
+        <v>57.8</v>
       </c>
       <c r="J19">
-        <v>24</v>
+        <v>61.1</v>
       </c>
       <c r="K19">
-        <v>15.2</v>
+        <v>65</v>
       </c>
       <c r="L19">
-        <v>7.1</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
@@ -436,37 +436,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46197</v>
+        <v>46260</v>
       </c>
       <c r="C1" s="1">
-        <v>46204</v>
+        <v>46267</v>
       </c>
       <c r="D1" s="1">
-        <v>46211</v>
+        <v>46274</v>
       </c>
       <c r="E1" s="1">
-        <v>46218</v>
+        <v>46281</v>
       </c>
       <c r="F1" s="1">
-        <v>46225</v>
+        <v>46288</v>
       </c>
       <c r="G1" s="1">
-        <v>46232</v>
+        <v>46295</v>
       </c>
       <c r="H1" s="1">
-        <v>46239</v>
+        <v>46302</v>
       </c>
       <c r="I1" s="1">
-        <v>46246</v>
+        <v>46309</v>
       </c>
       <c r="J1" s="1">
-        <v>46253</v>
+        <v>46316</v>
       </c>
       <c r="K1" s="1">
-        <v>46260</v>
+        <v>46323</v>
       </c>
       <c r="L1" s="1">
-        <v>46267</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -474,37 +474,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>60</v>
+        <v>49.2</v>
       </c>
       <c r="C2">
-        <v>58.5</v>
+        <v>49.6</v>
       </c>
       <c r="D2">
-        <v>57.2</v>
+        <v>49.9</v>
       </c>
       <c r="E2">
-        <v>56.5</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>56.4</v>
+        <v>49.8</v>
       </c>
       <c r="G2">
-        <v>57</v>
+        <v>49.2</v>
       </c>
       <c r="H2">
-        <v>58.4</v>
+        <v>48.4</v>
       </c>
       <c r="I2">
-        <v>60.3</v>
+        <v>47.3</v>
       </c>
       <c r="J2">
-        <v>62.6</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>65</v>
+        <v>44.6</v>
       </c>
       <c r="L2">
-        <v>67.3</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -512,37 +512,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63.5</v>
+        <v>50.9</v>
       </c>
       <c r="C3">
-        <v>61.6</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>59.8</v>
+        <v>48.7</v>
       </c>
       <c r="E3">
-        <v>58.2</v>
+        <v>47.1</v>
       </c>
       <c r="F3">
-        <v>56.9</v>
+        <v>45.1</v>
       </c>
       <c r="G3">
-        <v>56</v>
+        <v>42.8</v>
       </c>
       <c r="H3">
-        <v>55.5</v>
+        <v>40.2</v>
       </c>
       <c r="I3">
-        <v>55.1</v>
+        <v>37.6</v>
       </c>
       <c r="J3">
-        <v>54.9</v>
+        <v>35</v>
       </c>
       <c r="K3">
-        <v>54.7</v>
+        <v>32.5</v>
       </c>
       <c r="L3">
-        <v>54.4</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -550,37 +550,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>67.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="C4">
-        <v>69.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="D4">
-        <v>71.2</v>
+        <v>61.5</v>
       </c>
       <c r="E4">
-        <v>72.3</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>72.8</v>
+        <v>58.4</v>
       </c>
       <c r="G4">
-        <v>72.7</v>
+        <v>56.7</v>
       </c>
       <c r="H4">
-        <v>72.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="I4">
-        <v>70.90000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="J4">
-        <v>69.3</v>
+        <v>50.6</v>
       </c>
       <c r="K4">
-        <v>67.2</v>
+        <v>48.3</v>
       </c>
       <c r="L4">
-        <v>64.90000000000001</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -588,37 +588,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>52.9</v>
       </c>
       <c r="C5">
-        <v>61.3</v>
+        <v>53.5</v>
       </c>
       <c r="D5">
-        <v>59.7</v>
+        <v>53.8</v>
       </c>
       <c r="E5">
-        <v>58.6</v>
+        <v>53.6</v>
       </c>
       <c r="F5">
-        <v>58.3</v>
+        <v>52.6</v>
       </c>
       <c r="G5">
-        <v>58.9</v>
+        <v>50.9</v>
       </c>
       <c r="H5">
-        <v>60.3</v>
+        <v>48.4</v>
       </c>
       <c r="I5">
-        <v>62.5</v>
+        <v>45.3</v>
       </c>
       <c r="J5">
-        <v>65.3</v>
+        <v>41.8</v>
       </c>
       <c r="K5">
-        <v>68.3</v>
+        <v>38.1</v>
       </c>
       <c r="L5">
-        <v>71.09999999999999</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -626,37 +626,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>50.1</v>
+        <v>37.6</v>
       </c>
       <c r="C6">
-        <v>47.6</v>
+        <v>39.1</v>
       </c>
       <c r="D6">
-        <v>46.1</v>
+        <v>40.6</v>
       </c>
       <c r="E6">
-        <v>45.7</v>
+        <v>41.9</v>
       </c>
       <c r="F6">
-        <v>46.7</v>
+        <v>43.1</v>
       </c>
       <c r="G6">
-        <v>48.9</v>
+        <v>44</v>
       </c>
       <c r="H6">
-        <v>52.1</v>
+        <v>44.7</v>
       </c>
       <c r="I6">
-        <v>56.1</v>
+        <v>45.1</v>
       </c>
       <c r="J6">
-        <v>60.5</v>
+        <v>45.2</v>
       </c>
       <c r="K6">
-        <v>64.8</v>
+        <v>45.1</v>
       </c>
       <c r="L6">
-        <v>68.59999999999999</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -664,37 +664,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>59.6</v>
+        <v>48.6</v>
       </c>
       <c r="C7">
-        <v>56.9</v>
+        <v>48.5</v>
       </c>
       <c r="D7">
-        <v>54.5</v>
+        <v>48.1</v>
       </c>
       <c r="E7">
-        <v>52.3</v>
+        <v>47</v>
       </c>
       <c r="F7">
-        <v>50.6</v>
+        <v>45.4</v>
       </c>
       <c r="G7">
-        <v>49.5</v>
+        <v>43.2</v>
       </c>
       <c r="H7">
-        <v>49</v>
+        <v>40.4</v>
       </c>
       <c r="I7">
-        <v>48.9</v>
+        <v>37.3</v>
       </c>
       <c r="J7">
-        <v>49.2</v>
+        <v>34.1</v>
       </c>
       <c r="K7">
-        <v>49.7</v>
+        <v>30.9</v>
       </c>
       <c r="L7">
-        <v>50.3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -702,37 +702,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>52</v>
+        <v>48.1</v>
       </c>
       <c r="C8">
-        <v>49.8</v>
+        <v>48.7</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>48.9</v>
       </c>
       <c r="E8">
-        <v>47</v>
+        <v>48.5</v>
       </c>
       <c r="F8">
-        <v>46.9</v>
+        <v>47.5</v>
       </c>
       <c r="G8">
-        <v>47.6</v>
+        <v>45.9</v>
       </c>
       <c r="H8">
-        <v>49.2</v>
+        <v>43.8</v>
       </c>
       <c r="I8">
-        <v>51.3</v>
+        <v>41.5</v>
       </c>
       <c r="J8">
-        <v>53.8</v>
+        <v>39.1</v>
       </c>
       <c r="K8">
-        <v>56.3</v>
+        <v>36.8</v>
       </c>
       <c r="L8">
-        <v>58.6</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -740,37 +740,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>47.3</v>
+        <v>43.8</v>
       </c>
       <c r="C9">
-        <v>44.9</v>
+        <v>44</v>
       </c>
       <c r="D9">
-        <v>42.8</v>
+        <v>43.6</v>
       </c>
       <c r="E9">
-        <v>41.3</v>
+        <v>42.6</v>
       </c>
       <c r="F9">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="G9">
-        <v>40.3</v>
+        <v>38.5</v>
       </c>
       <c r="H9">
-        <v>40.8</v>
+        <v>35.7</v>
       </c>
       <c r="I9">
-        <v>41.8</v>
+        <v>32.6</v>
       </c>
       <c r="J9">
-        <v>43.1</v>
+        <v>29.5</v>
       </c>
       <c r="K9">
-        <v>44.6</v>
+        <v>26.6</v>
       </c>
       <c r="L9">
-        <v>46.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -778,37 +778,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="C10">
-        <v>53.8</v>
+        <v>51.8</v>
       </c>
       <c r="D10">
-        <v>53.9</v>
+        <v>52.8</v>
       </c>
       <c r="E10">
-        <v>54.4</v>
+        <v>53.6</v>
       </c>
       <c r="F10">
-        <v>55.6</v>
+        <v>54.2</v>
       </c>
       <c r="G10">
-        <v>57.5</v>
+        <v>54.6</v>
       </c>
       <c r="H10">
-        <v>60.1</v>
+        <v>54.6</v>
       </c>
       <c r="I10">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="J10">
-        <v>66.59999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="K10">
-        <v>70</v>
+        <v>52.6</v>
       </c>
       <c r="L10">
-        <v>73.09999999999999</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -816,37 +816,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>60.7</v>
+        <v>40.7</v>
       </c>
       <c r="C11">
-        <v>58.4</v>
+        <v>42.2</v>
       </c>
       <c r="D11">
-        <v>57</v>
+        <v>43.9</v>
       </c>
       <c r="E11">
-        <v>56.8</v>
+        <v>45.6</v>
       </c>
       <c r="F11">
-        <v>57.9</v>
+        <v>47.3</v>
       </c>
       <c r="G11">
-        <v>60.4</v>
+        <v>48.9</v>
       </c>
       <c r="H11">
-        <v>64.2</v>
+        <v>50.3</v>
       </c>
       <c r="I11">
-        <v>68.8</v>
+        <v>51.3</v>
       </c>
       <c r="J11">
-        <v>73.8</v>
+        <v>52</v>
       </c>
       <c r="K11">
-        <v>78.8</v>
+        <v>52.3</v>
       </c>
       <c r="L11">
-        <v>83.2</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -854,37 +854,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>63.9</v>
+        <v>59.3</v>
       </c>
       <c r="C12">
-        <v>63.6</v>
+        <v>59.2</v>
       </c>
       <c r="D12">
-        <v>63.3</v>
+        <v>58.7</v>
       </c>
       <c r="E12">
-        <v>63.1</v>
+        <v>57.7</v>
       </c>
       <c r="F12">
-        <v>63.1</v>
+        <v>56.2</v>
       </c>
       <c r="G12">
-        <v>63.4</v>
+        <v>54.2</v>
       </c>
       <c r="H12">
-        <v>63.9</v>
+        <v>51.7</v>
       </c>
       <c r="I12">
-        <v>64.7</v>
+        <v>48.8</v>
       </c>
       <c r="J12">
-        <v>65.7</v>
+        <v>45.6</v>
       </c>
       <c r="K12">
-        <v>66.59999999999999</v>
+        <v>42.3</v>
       </c>
       <c r="L12">
-        <v>67.40000000000001</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -892,37 +892,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>66.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="C13">
-        <v>66.09999999999999</v>
+        <v>51.3</v>
       </c>
       <c r="D13">
-        <v>65.3</v>
+        <v>50.2</v>
       </c>
       <c r="E13">
-        <v>64.7</v>
+        <v>49.1</v>
       </c>
       <c r="F13">
-        <v>64.2</v>
+        <v>48.1</v>
       </c>
       <c r="G13">
-        <v>63.9</v>
+        <v>47.1</v>
       </c>
       <c r="H13">
-        <v>63.7</v>
+        <v>46.3</v>
       </c>
       <c r="I13">
-        <v>63.4</v>
+        <v>45.7</v>
       </c>
       <c r="J13">
-        <v>62.9</v>
+        <v>45.1</v>
       </c>
       <c r="K13">
-        <v>62.2</v>
+        <v>44.7</v>
       </c>
       <c r="L13">
-        <v>61.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -930,37 +930,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>65.3</v>
+        <v>44.8</v>
       </c>
       <c r="C14">
-        <v>65.3</v>
+        <v>45.1</v>
       </c>
       <c r="D14">
-        <v>65.7</v>
+        <v>45.8</v>
       </c>
       <c r="E14">
-        <v>66.8</v>
+        <v>46.7</v>
       </c>
       <c r="F14">
-        <v>68.7</v>
+        <v>47.9</v>
       </c>
       <c r="G14">
-        <v>71.40000000000001</v>
+        <v>49.1</v>
       </c>
       <c r="H14">
-        <v>74.90000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="I14">
-        <v>78.90000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="J14">
-        <v>83.2</v>
+        <v>51.8</v>
       </c>
       <c r="K14">
-        <v>87.40000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="L14">
-        <v>91.09999999999999</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -968,37 +968,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>57.1</v>
+        <v>50.4</v>
       </c>
       <c r="C15">
-        <v>55.4</v>
+        <v>50.5</v>
       </c>
       <c r="D15">
-        <v>54</v>
+        <v>49.9</v>
       </c>
       <c r="E15">
-        <v>53.1</v>
+        <v>48.7</v>
       </c>
       <c r="F15">
-        <v>52.8</v>
+        <v>46.8</v>
       </c>
       <c r="G15">
-        <v>53.1</v>
+        <v>44.2</v>
       </c>
       <c r="H15">
-        <v>53.9</v>
+        <v>41</v>
       </c>
       <c r="I15">
-        <v>55.2</v>
+        <v>37.5</v>
       </c>
       <c r="J15">
-        <v>56.7</v>
+        <v>33.9</v>
       </c>
       <c r="K15">
-        <v>58.3</v>
+        <v>30.3</v>
       </c>
       <c r="L15">
-        <v>59.7</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1006,37 +1006,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>61.2</v>
+        <v>57.7</v>
       </c>
       <c r="C16">
-        <v>59.8</v>
+        <v>58.3</v>
       </c>
       <c r="D16">
         <v>58.7</v>
       </c>
       <c r="E16">
+        <v>58.7</v>
+      </c>
+      <c r="F16">
         <v>58.3</v>
       </c>
-      <c r="F16">
-        <v>58.6</v>
-      </c>
       <c r="G16">
-        <v>59.9</v>
+        <v>57.4</v>
       </c>
       <c r="H16">
-        <v>62.1</v>
+        <v>56.1</v>
       </c>
       <c r="I16">
-        <v>65.09999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="J16">
-        <v>68.5</v>
+        <v>52.8</v>
       </c>
       <c r="K16">
-        <v>72.2</v>
+        <v>51</v>
       </c>
       <c r="L16">
-        <v>75.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1044,37 +1044,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>62.9</v>
+        <v>42.5</v>
       </c>
       <c r="C17">
-        <v>62.7</v>
+        <v>43.4</v>
       </c>
       <c r="D17">
-        <v>63.2</v>
+        <v>44.8</v>
       </c>
       <c r="E17">
-        <v>64.90000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="F17">
-        <v>67.90000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="G17">
-        <v>72.40000000000001</v>
+        <v>50.5</v>
       </c>
       <c r="H17">
-        <v>78.09999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="I17">
-        <v>84.8</v>
+        <v>54.3</v>
       </c>
       <c r="J17">
-        <v>92</v>
+        <v>55.8</v>
       </c>
       <c r="K17">
-        <v>99.09999999999999</v>
+        <v>56.9</v>
       </c>
       <c r="L17">
-        <v>105.6</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1082,37 +1082,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>64.5</v>
+        <v>40</v>
       </c>
       <c r="C18">
-        <v>59.3</v>
+        <v>41.4</v>
       </c>
       <c r="D18">
-        <v>53.6</v>
+        <v>43.4</v>
       </c>
       <c r="E18">
-        <v>48.2</v>
+        <v>45.6</v>
       </c>
       <c r="F18">
-        <v>43.4</v>
+        <v>48</v>
       </c>
       <c r="G18">
-        <v>39.9</v>
+        <v>50.3</v>
       </c>
       <c r="H18">
-        <v>37.8</v>
+        <v>52.5</v>
       </c>
       <c r="I18">
-        <v>37.3</v>
+        <v>54.6</v>
       </c>
       <c r="J18">
-        <v>38.3</v>
+        <v>56.5</v>
       </c>
       <c r="K18">
-        <v>40.5</v>
+        <v>58.1</v>
       </c>
       <c r="L18">
-        <v>43.6</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1120,37 +1120,37 @@
         <v>17</v>
       </c>
       <c r="B19">
+        <v>51.5</v>
+      </c>
+      <c r="C19">
+        <v>53</v>
+      </c>
+      <c r="D19">
+        <v>54.6</v>
+      </c>
+      <c r="E19">
+        <v>56.2</v>
+      </c>
+      <c r="F19">
+        <v>57.5</v>
+      </c>
+      <c r="G19">
+        <v>58.5</v>
+      </c>
+      <c r="H19">
+        <v>59.3</v>
+      </c>
+      <c r="I19">
         <v>59.8</v>
       </c>
-      <c r="C19">
-        <v>57.8</v>
-      </c>
-      <c r="D19">
-        <v>55.9</v>
-      </c>
-      <c r="E19">
-        <v>54.4</v>
-      </c>
-      <c r="F19">
-        <v>53.6</v>
-      </c>
-      <c r="G19">
-        <v>53.9</v>
-      </c>
-      <c r="H19">
-        <v>55.3</v>
-      </c>
-      <c r="I19">
-        <v>57.8</v>
-      </c>
       <c r="J19">
-        <v>61.1</v>
+        <v>60.1</v>
       </c>
       <c r="K19">
-        <v>65</v>
+        <v>60.3</v>
       </c>
       <c r="L19">
-        <v>68.90000000000001</v>
+        <v>60.3</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_3/VCI3M_Forecast_Overview_CLUSTER_3.xlsx
@@ -436,37 +436,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46260</v>
+        <v>46281</v>
       </c>
       <c r="C1" s="1">
-        <v>46267</v>
+        <v>46288</v>
       </c>
       <c r="D1" s="1">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="E1" s="1">
-        <v>46281</v>
+        <v>46302</v>
       </c>
       <c r="F1" s="1">
-        <v>46288</v>
+        <v>46309</v>
       </c>
       <c r="G1" s="1">
-        <v>46295</v>
+        <v>46316</v>
       </c>
       <c r="H1" s="1">
-        <v>46302</v>
+        <v>46323</v>
       </c>
       <c r="I1" s="1">
-        <v>46309</v>
+        <v>46330</v>
       </c>
       <c r="J1" s="1">
-        <v>46316</v>
+        <v>46337</v>
       </c>
       <c r="K1" s="1">
-        <v>46323</v>
+        <v>46344</v>
       </c>
       <c r="L1" s="1">
-        <v>46330</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -474,37 +474,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>49.2</v>
+        <v>50.5</v>
       </c>
       <c r="C2">
+        <v>50.7</v>
+      </c>
+      <c r="D2">
+        <v>50.6</v>
+      </c>
+      <c r="E2">
+        <v>50.4</v>
+      </c>
+      <c r="F2">
+        <v>50.1</v>
+      </c>
+      <c r="G2">
         <v>49.6</v>
       </c>
-      <c r="D2">
-        <v>49.9</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <v>49.8</v>
-      </c>
-      <c r="G2">
-        <v>49.2</v>
-      </c>
       <c r="H2">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="I2">
+        <v>48.5</v>
+      </c>
+      <c r="J2">
+        <v>48.1</v>
+      </c>
+      <c r="K2">
+        <v>47.6</v>
+      </c>
+      <c r="L2">
         <v>47.3</v>
-      </c>
-      <c r="J2">
-        <v>46</v>
-      </c>
-      <c r="K2">
-        <v>44.6</v>
-      </c>
-      <c r="L2">
-        <v>43.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -512,37 +512,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>50.9</v>
+        <v>49.5</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="D3">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>47.1</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>45.1</v>
+        <v>49.2</v>
       </c>
       <c r="G3">
-        <v>42.8</v>
+        <v>49.7</v>
       </c>
       <c r="H3">
-        <v>40.2</v>
+        <v>50.5</v>
       </c>
       <c r="I3">
-        <v>37.6</v>
+        <v>51.4</v>
       </c>
       <c r="J3">
-        <v>35</v>
+        <v>52.6</v>
       </c>
       <c r="K3">
-        <v>32.5</v>
+        <v>53.8</v>
       </c>
       <c r="L3">
-        <v>30.4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -550,37 +550,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>64.09999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="C4">
-        <v>62.9</v>
+        <v>57.1</v>
       </c>
       <c r="D4">
-        <v>61.5</v>
+        <v>54.7</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>58.4</v>
+        <v>49.1</v>
       </c>
       <c r="G4">
-        <v>56.7</v>
+        <v>46</v>
       </c>
       <c r="H4">
-        <v>54.8</v>
+        <v>42.7</v>
       </c>
       <c r="I4">
-        <v>52.8</v>
+        <v>39.4</v>
       </c>
       <c r="J4">
-        <v>50.6</v>
+        <v>36.3</v>
       </c>
       <c r="K4">
-        <v>48.3</v>
+        <v>33.4</v>
       </c>
       <c r="L4">
-        <v>45.9</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -588,37 +588,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>52.9</v>
+        <v>55.1</v>
       </c>
       <c r="C5">
-        <v>53.5</v>
+        <v>55.4</v>
       </c>
       <c r="D5">
-        <v>53.8</v>
+        <v>55.4</v>
       </c>
       <c r="E5">
-        <v>53.6</v>
+        <v>55</v>
       </c>
       <c r="F5">
-        <v>52.6</v>
+        <v>54.5</v>
       </c>
       <c r="G5">
-        <v>50.9</v>
+        <v>53.7</v>
       </c>
       <c r="H5">
-        <v>48.4</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>45.3</v>
+        <v>52.4</v>
       </c>
       <c r="J5">
-        <v>41.8</v>
+        <v>52</v>
       </c>
       <c r="K5">
-        <v>38.1</v>
+        <v>51.8</v>
       </c>
       <c r="L5">
-        <v>34.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -626,37 +626,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>37.6</v>
+        <v>41</v>
       </c>
       <c r="C6">
-        <v>39.1</v>
+        <v>41.8</v>
       </c>
       <c r="D6">
-        <v>40.6</v>
+        <v>42.2</v>
       </c>
       <c r="E6">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="F6">
-        <v>43.1</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>44</v>
+        <v>41.6</v>
       </c>
       <c r="H6">
-        <v>44.7</v>
+        <v>40.9</v>
       </c>
       <c r="I6">
-        <v>45.1</v>
+        <v>40.2</v>
       </c>
       <c r="J6">
-        <v>45.2</v>
+        <v>39.4</v>
       </c>
       <c r="K6">
-        <v>45.1</v>
+        <v>38.6</v>
       </c>
       <c r="L6">
-        <v>44.7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -664,37 +664,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="C7">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="D7">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="E7">
+        <v>47.1</v>
+      </c>
+      <c r="F7">
+        <v>46.4</v>
+      </c>
+      <c r="G7">
+        <v>45.8</v>
+      </c>
+      <c r="H7">
+        <v>45.4</v>
+      </c>
+      <c r="I7">
+        <v>45.3</v>
+      </c>
+      <c r="J7">
+        <v>45.5</v>
+      </c>
+      <c r="K7">
+        <v>46.1</v>
+      </c>
+      <c r="L7">
         <v>47</v>
-      </c>
-      <c r="F7">
-        <v>45.4</v>
-      </c>
-      <c r="G7">
-        <v>43.2</v>
-      </c>
-      <c r="H7">
-        <v>40.4</v>
-      </c>
-      <c r="I7">
-        <v>37.3</v>
-      </c>
-      <c r="J7">
-        <v>34.1</v>
-      </c>
-      <c r="K7">
-        <v>30.9</v>
-      </c>
-      <c r="L7">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -702,37 +702,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>48.1</v>
+        <v>50.1</v>
       </c>
       <c r="C8">
-        <v>48.7</v>
+        <v>50.3</v>
       </c>
       <c r="D8">
-        <v>48.9</v>
+        <v>50.3</v>
       </c>
       <c r="E8">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
       <c r="F8">
-        <v>47.5</v>
+        <v>50.2</v>
       </c>
       <c r="G8">
-        <v>45.9</v>
+        <v>50.3</v>
       </c>
       <c r="H8">
-        <v>43.8</v>
+        <v>50.6</v>
       </c>
       <c r="I8">
-        <v>41.5</v>
+        <v>51.1</v>
       </c>
       <c r="J8">
-        <v>39.1</v>
+        <v>51.9</v>
       </c>
       <c r="K8">
-        <v>36.8</v>
+        <v>52.9</v>
       </c>
       <c r="L8">
-        <v>34.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -740,37 +740,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>43.8</v>
+        <v>45.2</v>
       </c>
       <c r="C9">
-        <v>44</v>
+        <v>45.2</v>
       </c>
       <c r="D9">
-        <v>43.6</v>
+        <v>45.2</v>
       </c>
       <c r="E9">
-        <v>42.6</v>
+        <v>45.1</v>
       </c>
       <c r="F9">
-        <v>40.9</v>
+        <v>45.1</v>
       </c>
       <c r="G9">
-        <v>38.5</v>
+        <v>45.4</v>
       </c>
       <c r="H9">
-        <v>35.7</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>32.6</v>
+        <v>46.9</v>
       </c>
       <c r="J9">
-        <v>29.5</v>
+        <v>48.2</v>
       </c>
       <c r="K9">
-        <v>26.6</v>
+        <v>49.8</v>
       </c>
       <c r="L9">
-        <v>24.2</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -778,37 +778,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>50.8</v>
+        <v>53.5</v>
       </c>
       <c r="C10">
-        <v>51.8</v>
+        <v>53.8</v>
       </c>
       <c r="D10">
-        <v>52.8</v>
+        <v>53.6</v>
       </c>
       <c r="E10">
-        <v>53.6</v>
+        <v>52.9</v>
       </c>
       <c r="F10">
-        <v>54.2</v>
+        <v>51.7</v>
       </c>
       <c r="G10">
-        <v>54.6</v>
+        <v>50</v>
       </c>
       <c r="H10">
-        <v>54.6</v>
+        <v>47.9</v>
       </c>
       <c r="I10">
-        <v>54.2</v>
+        <v>45.4</v>
       </c>
       <c r="J10">
-        <v>53.5</v>
+        <v>42.9</v>
       </c>
       <c r="K10">
-        <v>52.6</v>
+        <v>40.3</v>
       </c>
       <c r="L10">
-        <v>51.4</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -816,37 +816,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>40.7</v>
+        <v>44.6</v>
       </c>
       <c r="C11">
-        <v>42.2</v>
+        <v>45.8</v>
       </c>
       <c r="D11">
-        <v>43.9</v>
+        <v>46.7</v>
       </c>
       <c r="E11">
+        <v>47.4</v>
+      </c>
+      <c r="F11">
+        <v>47.7</v>
+      </c>
+      <c r="G11">
+        <v>47.7</v>
+      </c>
+      <c r="H11">
+        <v>47.3</v>
+      </c>
+      <c r="I11">
+        <v>46.6</v>
+      </c>
+      <c r="J11">
         <v>45.6</v>
       </c>
-      <c r="F11">
-        <v>47.3</v>
-      </c>
-      <c r="G11">
-        <v>48.9</v>
-      </c>
-      <c r="H11">
-        <v>50.3</v>
-      </c>
-      <c r="I11">
-        <v>51.3</v>
-      </c>
-      <c r="J11">
-        <v>52</v>
-      </c>
       <c r="K11">
-        <v>52.3</v>
+        <v>44.5</v>
       </c>
       <c r="L11">
-        <v>52.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -857,34 +857,34 @@
         <v>59.3</v>
       </c>
       <c r="C12">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="D12">
-        <v>58.7</v>
+        <v>58.4</v>
       </c>
       <c r="E12">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="F12">
-        <v>56.2</v>
+        <v>56.7</v>
       </c>
       <c r="G12">
-        <v>54.2</v>
+        <v>55.7</v>
       </c>
       <c r="H12">
-        <v>51.7</v>
+        <v>54.7</v>
       </c>
       <c r="I12">
-        <v>48.8</v>
+        <v>53.8</v>
       </c>
       <c r="J12">
-        <v>45.6</v>
+        <v>53.1</v>
       </c>
       <c r="K12">
-        <v>42.3</v>
+        <v>52.5</v>
       </c>
       <c r="L12">
-        <v>39.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -892,37 +892,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>52.4</v>
+        <v>50.3</v>
       </c>
       <c r="C13">
-        <v>51.3</v>
+        <v>50.1</v>
       </c>
       <c r="D13">
         <v>50.2</v>
       </c>
       <c r="E13">
-        <v>49.1</v>
+        <v>50.7</v>
       </c>
       <c r="F13">
-        <v>48.1</v>
+        <v>51.5</v>
       </c>
       <c r="G13">
-        <v>47.1</v>
+        <v>52.5</v>
       </c>
       <c r="H13">
-        <v>46.3</v>
+        <v>53.7</v>
       </c>
       <c r="I13">
-        <v>45.7</v>
+        <v>55</v>
       </c>
       <c r="J13">
-        <v>45.1</v>
+        <v>56.1</v>
       </c>
       <c r="K13">
-        <v>44.7</v>
+        <v>57.2</v>
       </c>
       <c r="L13">
-        <v>44.4</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -930,37 +930,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>44.8</v>
+        <v>45.4</v>
       </c>
       <c r="C14">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="D14">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="E14">
-        <v>46.7</v>
+        <v>45.9</v>
       </c>
       <c r="F14">
-        <v>47.9</v>
+        <v>45.6</v>
       </c>
       <c r="G14">
-        <v>49.1</v>
+        <v>45</v>
       </c>
       <c r="H14">
-        <v>50.2</v>
+        <v>44</v>
       </c>
       <c r="I14">
-        <v>51.2</v>
+        <v>42.6</v>
       </c>
       <c r="J14">
-        <v>51.8</v>
+        <v>41.1</v>
       </c>
       <c r="K14">
-        <v>52.1</v>
+        <v>39.3</v>
       </c>
       <c r="L14">
-        <v>52</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -968,37 +968,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="C15">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="D15">
+        <v>50.1</v>
+      </c>
+      <c r="E15">
+        <v>49.5</v>
+      </c>
+      <c r="F15">
+        <v>48.9</v>
+      </c>
+      <c r="G15">
+        <v>48.4</v>
+      </c>
+      <c r="H15">
+        <v>48.1</v>
+      </c>
+      <c r="I15">
+        <v>48.1</v>
+      </c>
+      <c r="J15">
+        <v>48.4</v>
+      </c>
+      <c r="K15">
+        <v>49</v>
+      </c>
+      <c r="L15">
         <v>49.9</v>
-      </c>
-      <c r="E15">
-        <v>48.7</v>
-      </c>
-      <c r="F15">
-        <v>46.8</v>
-      </c>
-      <c r="G15">
-        <v>44.2</v>
-      </c>
-      <c r="H15">
-        <v>41</v>
-      </c>
-      <c r="I15">
-        <v>37.5</v>
-      </c>
-      <c r="J15">
-        <v>33.9</v>
-      </c>
-      <c r="K15">
-        <v>30.3</v>
-      </c>
-      <c r="L15">
-        <v>27.1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1006,37 +1006,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>57.7</v>
+        <v>59.2</v>
       </c>
       <c r="C16">
-        <v>58.3</v>
+        <v>59.1</v>
       </c>
       <c r="D16">
         <v>58.7</v>
       </c>
       <c r="E16">
-        <v>58.7</v>
+        <v>57.9</v>
       </c>
       <c r="F16">
-        <v>58.3</v>
+        <v>56.9</v>
       </c>
       <c r="G16">
-        <v>57.4</v>
+        <v>55.7</v>
       </c>
       <c r="H16">
-        <v>56.1</v>
+        <v>54.5</v>
       </c>
       <c r="I16">
-        <v>54.6</v>
+        <v>53.3</v>
       </c>
       <c r="J16">
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
       <c r="K16">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="L16">
-        <v>49.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1044,37 +1044,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>42.5</v>
+        <v>44.8</v>
       </c>
       <c r="C17">
-        <v>43.4</v>
+        <v>45.8</v>
       </c>
       <c r="D17">
-        <v>44.8</v>
+        <v>46.6</v>
       </c>
       <c r="E17">
-        <v>46.6</v>
+        <v>47.1</v>
       </c>
       <c r="F17">
-        <v>48.5</v>
+        <v>47.4</v>
       </c>
       <c r="G17">
-        <v>50.5</v>
+        <v>47.4</v>
       </c>
       <c r="H17">
-        <v>52.5</v>
+        <v>47.1</v>
       </c>
       <c r="I17">
-        <v>54.3</v>
+        <v>46.5</v>
       </c>
       <c r="J17">
-        <v>55.8</v>
+        <v>45.6</v>
       </c>
       <c r="K17">
-        <v>56.9</v>
+        <v>44.7</v>
       </c>
       <c r="L17">
-        <v>57.7</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1082,37 +1082,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>41.4</v>
+        <v>46.8</v>
       </c>
       <c r="D18">
-        <v>43.4</v>
+        <v>48.4</v>
       </c>
       <c r="E18">
-        <v>45.6</v>
+        <v>49.8</v>
       </c>
       <c r="F18">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="G18">
-        <v>50.3</v>
+        <v>51.6</v>
       </c>
       <c r="H18">
+        <v>52.2</v>
+      </c>
+      <c r="I18">
         <v>52.5</v>
       </c>
-      <c r="I18">
-        <v>54.6</v>
-      </c>
       <c r="J18">
-        <v>56.5</v>
+        <v>52.6</v>
       </c>
       <c r="K18">
-        <v>58.1</v>
+        <v>52.4</v>
       </c>
       <c r="L18">
-        <v>59.6</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1120,37 +1120,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>51.5</v>
+        <v>56</v>
       </c>
       <c r="C19">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D19">
-        <v>54.6</v>
+        <v>57.5</v>
       </c>
       <c r="E19">
-        <v>56.2</v>
+        <v>57.6</v>
       </c>
       <c r="F19">
-        <v>57.5</v>
+        <v>57.2</v>
       </c>
       <c r="G19">
-        <v>58.5</v>
+        <v>56.6</v>
       </c>
       <c r="H19">
-        <v>59.3</v>
+        <v>55.7</v>
       </c>
       <c r="I19">
-        <v>59.8</v>
+        <v>54.7</v>
       </c>
       <c r="J19">
-        <v>60.1</v>
+        <v>53.6</v>
       </c>
       <c r="K19">
-        <v>60.3</v>
+        <v>52.5</v>
       </c>
       <c r="L19">
-        <v>60.3</v>
+        <v>51.4</v>
       </c>
     </row>
   </sheetData>
